--- a/backtest_runs/20260410_193731/by_symbol/JGICL/JGICL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JGICL/JGICL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2250.959999999995</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100366.12</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100366.12</v>
@@ -817,7 +817,7 @@
         <v>-813.5999999999923</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>107498.68</v>
@@ -863,7 +863,7 @@
         <v>-379.6800000000015</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>107119</v>
@@ -909,7 +909,7 @@
         <v>-2630.639999999997</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>104488.36</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>104488.36</v>
@@ -1093,7 +1093,7 @@
         <v>-12109.08000000001</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>96854.07999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-3240.840000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>96352.35999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-4081.559999999997</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>92270.79999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-244.0799999999996</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>92026.71999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-2996.760000000001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>91036.84</v>
@@ -1461,7 +1461,7 @@
         <v>-678</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>90358.84</v>
@@ -1553,7 +1553,7 @@
         <v>-447.4799999999977</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>89911.36</v>
@@ -1645,7 +1645,7 @@
         <v>-135.5999999999923</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>94020.03999999999</v>
